--- a/Assets/@Resources/Data/Excel/MissionData.xlsx
+++ b/Assets/@Resources/Data/Excel/MissionData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -782,41 +782,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2001</v>
+        <v>1008</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DungeonClear</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BossClear</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>20</v>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Crystal</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionDungeonFormat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -824,15 +824,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -878,13 +878,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -892,15 +892,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DailyAllClear</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -912,13 +912,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MissionDailyAllFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DailyAllClear</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>5</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KillMonster</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1500</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -946,29 +946,29 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MissionKillFormat</t>
+          <t>MissionDailyAllFormat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3001</v>
+        <v>2005</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>KillMonster</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -976,17 +976,17 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionKillFormat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -994,11 +994,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1010,17 +1010,17 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1048,13 +1048,13 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1062,15 +1062,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1096,15 +1096,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1116,13 +1116,13 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1130,15 +1130,15 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1180,17 +1180,17 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1198,15 +1198,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1214,17 +1214,17 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MissionEnhanceFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1232,15 +1232,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1248,17 +1248,17 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionEnhanceFormat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1266,15 +1266,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1300,15 +1300,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1320,13 +1320,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1350,17 +1350,17 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1368,15 +1368,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1402,15 +1402,15 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1422,13 +1422,13 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1452,17 +1452,17 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1470,15 +1470,15 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1504,15 +1504,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1520,17 +1520,17 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1538,15 +1538,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1554,17 +1554,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1572,15 +1572,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1588,17 +1588,17 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MissionEnhanceFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1606,15 +1606,15 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1622,17 +1622,17 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionEnhanceFormat</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1640,15 +1640,15 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1674,15 +1674,15 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1708,15 +1708,15 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23</v>
+        <v>220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1724,17 +1724,17 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1742,15 +1742,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1776,15 +1776,15 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>240</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>25</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ReachLevel</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>70</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1810,33 +1810,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E41" t="n">
+        <v>70</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>100</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>120</v>
-      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1844,11 +1844,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1860,17 +1860,17 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1878,15 +1878,15 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>28</v>
+        <v>270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1894,17 +1894,17 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1912,15 +1912,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>280</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1932,13 +1932,13 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1946,15 +1946,15 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1966,13 +1966,13 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1980,15 +1980,15 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>31</v>
+        <v>300</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1996,17 +1996,17 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2014,15 +2014,15 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>32</v>
+        <v>310</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2034,13 +2034,13 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2048,15 +2048,15 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2082,15 +2082,15 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34</v>
+        <v>330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2116,15 +2116,15 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2132,17 +2132,17 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2150,15 +2150,15 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>36</v>
+        <v>350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2170,13 +2170,13 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2184,15 +2184,15 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37</v>
+        <v>360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2200,17 +2200,17 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2218,15 +2218,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2252,15 +2252,15 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2272,13 +2272,13 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2286,15 +2286,15 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>40</v>
+        <v>390</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2306,29 +2306,29 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4001</v>
+        <v>3040</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2336,33 +2336,33 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>AttendanceDayFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4002</v>
+        <v>3101</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>DungeonClear</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2370,17 +2370,17 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>AttendanceDayFormat</t>
+          <t>MissionDungeonFormat</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2396,15 +2396,15 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mandrake</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2464,15 +2464,15 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Mandrake</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2516,33 +2516,101 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>4005</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>50</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AttendanceDayFormat</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4006</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>50</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>AttendanceDayFormat</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
         <v>4007</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C64" t="n">
         <v>7</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E64" t="n">
         <v>7</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>300</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>AttendanceDayFormat</t>
         </is>

--- a/Assets/@Resources/Data/Excel/MissionData.xlsx
+++ b/Assets/@Resources/Data/Excel/MissionData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -816,41 +816,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2001</v>
+        <v>1009</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BondRequest</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BossClear</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>20</v>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Crystal</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionBondFormat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -858,15 +858,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -892,11 +892,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -912,13 +912,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DailyAllClear</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -946,13 +946,13 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MissionDailyAllFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -960,15 +960,15 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DailyAllClear</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>KillMonster</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -980,29 +980,29 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MissionKillFormat</t>
+          <t>MissionDailyAllFormat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3001</v>
+        <v>2005</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>KillMonster</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1010,17 +1010,17 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionKillFormat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1044,17 +1044,17 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1082,13 +1082,13 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1096,15 +1096,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1116,13 +1116,13 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1130,15 +1130,15 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1198,15 +1198,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1214,17 +1214,17 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1232,15 +1232,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1248,17 +1248,17 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MissionEnhanceFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1266,15 +1266,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1282,17 +1282,17 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionEnhanceFormat</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1300,15 +1300,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1320,13 +1320,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1354,13 +1354,13 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1368,15 +1368,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1402,15 +1402,15 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1422,13 +1422,13 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1436,15 +1436,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1456,13 +1456,13 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1470,11 +1470,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1486,17 +1486,17 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1504,15 +1504,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1520,17 +1520,17 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1538,15 +1538,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1554,17 +1554,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1572,15 +1572,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1588,17 +1588,17 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1606,15 +1606,15 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1622,17 +1622,17 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MissionEnhanceFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1640,15 +1640,15 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1656,17 +1656,17 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionEnhanceFormat</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1674,15 +1674,15 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1708,15 +1708,15 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1728,13 +1728,13 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MissionTrainFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1742,15 +1742,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BossClear</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1758,17 +1758,17 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MissionBossFormat</t>
+          <t>MissionTrainFormat</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1776,15 +1776,15 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>BossClear</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionBossFormat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1830,13 +1830,13 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1844,33 +1844,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E42" t="n">
+        <v>70</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>100</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>120</v>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1894,17 +1894,17 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MissionParryFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1912,15 +1912,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1928,17 +1928,17 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionParryFormat</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1946,15 +1946,15 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1966,13 +1966,13 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1980,15 +1980,15 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CaptureTry</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2000,13 +2000,13 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MissionCaptureFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2014,15 +2014,15 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>CaptureTry</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2030,17 +2030,17 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionCaptureFormat</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2048,15 +2048,15 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2082,15 +2082,15 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MissionDiscoverFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2116,15 +2116,15 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>Discover</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionDiscoverFormat</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2150,15 +2150,15 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2166,17 +2166,17 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2184,15 +2184,15 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2218,15 +2218,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2252,15 +2252,15 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2268,17 +2268,17 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2286,15 +2286,15 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ReachLevel</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MissionLevelFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2320,15 +2320,15 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NewStage</t>
+          <t>ReachLevel</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MissionStageFormat</t>
+          <t>MissionLevelFormat</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3101</v>
+        <v>3040</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2354,15 +2354,15 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>25</v>
+        <v>400</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DungeonClear</t>
+          <t>NewStage</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2370,29 +2370,29 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MissionDungeonFormat</t>
+          <t>MissionStageFormat</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4001</v>
+        <v>3101</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>DungeonClear</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2404,33 +2404,33 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AttendanceDayFormat</t>
+          <t>MissionDungeonFormat</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4002</v>
+        <v>3102</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>BondRequest</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2438,17 +2438,17 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AttendanceDayFormat</t>
+          <t>MissionBondFormat</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2464,15 +2464,15 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mandrake</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2532,15 +2532,15 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Mandrake</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2584,33 +2584,101 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>4005</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>50</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AttendanceDayFormat</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4006</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AttendanceDayFormat</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
         <v>4007</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C66" t="n">
         <v>7</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E66" t="n">
         <v>7</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>300</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>AttendanceDayFormat</t>
         </is>

--- a/Assets/@Resources/Data/Excel/MissionData.xlsx
+++ b/Assets/@Resources/Data/Excel/MissionData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,21 @@
           <t>TitleKey</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PremiumType</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PremiumValue</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>HonorKey</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +514,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -539,6 +569,21 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>제목 로컬라이즈 키({0}=목표)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>프리미엄 보상(Pass)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>프리미엄 보상량</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>칭호 로컬라이즈 키(Achieve)</t>
         </is>
       </c>
     </row>
@@ -575,6 +620,9 @@
           <t>MissionKillFormat</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -609,6 +657,9 @@
           <t>MissionBossFormat</t>
         </is>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -643,6 +694,9 @@
           <t>MissionTrainFormat</t>
         </is>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -677,6 +731,9 @@
           <t>MissionCaptureFormat</t>
         </is>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -711,6 +768,9 @@
           <t>MissionEnhanceFormat</t>
         </is>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -745,6 +805,9 @@
           <t>MissionParryFormat</t>
         </is>
       </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -779,6 +842,9 @@
           <t>MissionDailyChestText</t>
         </is>
       </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -813,6 +879,9 @@
           <t>MissionDungeonFormat</t>
         </is>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -847,6 +916,9 @@
           <t>MissionBondFormat</t>
         </is>
       </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -881,6 +953,9 @@
           <t>MissionBossFormat</t>
         </is>
       </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -915,6 +990,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -949,6 +1027,9 @@
           <t>MissionCaptureFormat</t>
         </is>
       </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -983,6 +1064,9 @@
           <t>MissionDailyAllFormat</t>
         </is>
       </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1017,6 +1101,9 @@
           <t>MissionKillFormat</t>
         </is>
       </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1051,6 +1138,9 @@
           <t>MissionTrainFormat</t>
         </is>
       </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1085,6 +1175,9 @@
           <t>MissionBossFormat</t>
         </is>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1119,6 +1212,9 @@
           <t>MissionParryFormat</t>
         </is>
       </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1153,6 +1249,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1187,6 +1286,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1221,6 +1323,9 @@
           <t>MissionCaptureFormat</t>
         </is>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1255,6 +1360,9 @@
           <t>MissionDiscoverFormat</t>
         </is>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1289,6 +1397,9 @@
           <t>MissionEnhanceFormat</t>
         </is>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1323,6 +1434,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1357,6 +1471,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1391,6 +1508,9 @@
           <t>MissionTrainFormat</t>
         </is>
       </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1425,6 +1545,9 @@
           <t>MissionDiscoverFormat</t>
         </is>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1459,6 +1582,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1493,6 +1619,9 @@
           <t>MissionBossFormat</t>
         </is>
       </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1527,6 +1656,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1561,6 +1693,9 @@
           <t>MissionParryFormat</t>
         </is>
       </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1595,6 +1730,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1629,6 +1767,9 @@
           <t>MissionDiscoverFormat</t>
         </is>
       </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1663,6 +1804,9 @@
           <t>MissionEnhanceFormat</t>
         </is>
       </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1697,6 +1841,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1731,6 +1878,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1765,6 +1915,9 @@
           <t>MissionTrainFormat</t>
         </is>
       </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1799,6 +1952,9 @@
           <t>MissionBossFormat</t>
         </is>
       </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1833,6 +1989,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1867,6 +2026,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1901,6 +2063,9 @@
           <t>MissionDiscoverFormat</t>
         </is>
       </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1935,6 +2100,9 @@
           <t>MissionParryFormat</t>
         </is>
       </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1969,6 +2137,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2003,6 +2174,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2037,6 +2211,9 @@
           <t>MissionCaptureFormat</t>
         </is>
       </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2071,6 +2248,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2105,6 +2285,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2139,6 +2322,9 @@
           <t>MissionDiscoverFormat</t>
         </is>
       </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2173,6 +2359,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2207,6 +2396,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2241,6 +2433,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2275,6 +2470,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2309,6 +2507,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2343,6 +2544,9 @@
           <t>MissionLevelFormat</t>
         </is>
       </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2377,6 +2581,9 @@
           <t>MissionStageFormat</t>
         </is>
       </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2411,6 +2618,9 @@
           <t>MissionDungeonFormat</t>
         </is>
       </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2445,6 +2655,9 @@
           <t>MissionBondFormat</t>
         </is>
       </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2479,6 +2692,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2513,6 +2729,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2547,6 +2766,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2581,6 +2803,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2615,6 +2840,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2649,6 +2877,9 @@
           <t>AttendanceDayFormat</t>
         </is>
       </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2682,6 +2913,1059 @@
         <is>
           <t>AttendanceDayFormat</t>
         </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6001</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>20</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6002</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>20</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6003</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6004</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>20</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6005</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mandrake</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6006</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>6007</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>35</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>6008</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>40</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>20</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>6009</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>45</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>6010</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>50</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mandrake</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6011</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>11</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>55</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>20</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6012</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>60</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>6013</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>13</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>65</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>20</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>6014</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>14</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>70</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>20</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>6015</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>15</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>75</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mandrake</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>6016</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>16</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>80</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>6017</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>17</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>85</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>20</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>6018</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>18</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>90</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>6019</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>19</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>95</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>6020</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>20</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mandrake</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>6021</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>105</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>20</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>6022</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>22</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>110</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>20</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>6023</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>23</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>115</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>6024</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>24</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>120</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>20</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>6025</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>25</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>125</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mandrake</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/MissionData.xlsx
+++ b/Assets/@Resources/Data/Excel/MissionData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3968,6 +3968,1756 @@
         <v>150</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7011</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>10</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>7012</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>HonorHunterText</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>7013</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>13</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>60</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>7014</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>14</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>100</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>HonorSlayerText</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>7015</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>200</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>HonorLegendText</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>7021</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>21</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BossClear</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>20</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>MissionBossFormat</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>7022</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>22</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BossClear</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>50</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>MissionBossFormat</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>HonorBossHunterText</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>7023</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>23</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BossClear</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>200</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>100</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MissionBossFormat</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>7024</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>24</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BossClear</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>500</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>200</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>MissionBossFormat</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>7031</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>31</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>20</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>7032</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>32</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>30</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>50</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>HonorPioneerText</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>7033</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>33</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>60</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>80</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>7034</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>34</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>120</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>7035</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>35</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NewStage</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>125</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>300</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>HonorConquerorText</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>7041</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>41</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ReachLevel</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>50</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>MissionLevelFormat</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>7042</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>42</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ReachLevel</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>60</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>MissionLevelFormat</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>7043</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>43</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ReachLevel</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>200</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>120</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>MissionLevelFormat</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>7044</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>44</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ReachLevel</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>300</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>300</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>MissionLevelFormat</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>HonorMaxText</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>7051</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>51</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Discover</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>50</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>MissionDiscoverFormat</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7052</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>52</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Discover</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>150</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>80</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>MissionDiscoverFormat</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>HonorScholarText</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>7053</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>53</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Discover</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>300</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>150</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>MissionDiscoverFormat</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>7054</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>54</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Discover</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>503</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>300</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>MissionDiscoverFormat</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>HonorCodexText</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>7061</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>61</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CaptureTry</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>20</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>MissionCaptureFormat</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>7062</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>62</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CaptureTry</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>50</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>50</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>MissionCaptureFormat</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>HonorTamerText</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>7063</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>63</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CaptureTry</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>200</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>120</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>MissionCaptureFormat</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>7071</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>71</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>20</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>20</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>MissionParryFormat</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>7072</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>72</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>50</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>MissionParryFormat</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>HonorParryText</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>7073</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>73</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>500</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>100</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>MissionParryFormat</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>7074</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>74</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>200</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>MissionParryFormat</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>HonorIronWallText</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>7081</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>81</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>50</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>MissionTrainFormat</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>7082</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>82</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>300</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>30</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>MissionTrainFormat</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>7083</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>83</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>60</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>MissionTrainFormat</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>HonorGrinderText</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>7084</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>84</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>150</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>MissionTrainFormat</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>7091</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>91</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Enhance</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>10</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>20</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>MissionEnhanceFormat</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>7092</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>92</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Enhance</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>50</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>50</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>MissionEnhanceFormat</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>HonorSmithText</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>7093</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>93</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Enhance</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>200</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>120</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>MissionEnhanceFormat</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>101</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DungeonClear</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>20</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>MissionDungeonFormat</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>102</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DungeonClear</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>50</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>60</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>MissionDungeonFormat</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>HonorDungeonText</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>103</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DungeonClear</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>200</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>150</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>MissionDungeonFormat</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>111</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BondRequest</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>20</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>MissionBondFormat</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7112</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>112</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BondRequest</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>50</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>60</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>MissionBondFormat</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>HonorFixerText</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>7113</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>113</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BondRequest</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>150</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>150</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>MissionBondFormat</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>7121</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>121</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DailyAllClear</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>7</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>MissionDailyAllFormat</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>7122</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>122</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DailyAllClear</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>30</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>80</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>MissionDailyAllFormat</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>HonorDiligentText</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>7123</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>123</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DailyAllClear</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>100</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>200</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>MissionDailyAllFormat</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
